--- a/2024AIDataScienceGNRGeneral/Advanced Excel/jan25.xlsx
+++ b/2024AIDataScienceGNRGeneral/Advanced Excel/jan25.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4CFB1B8-4346-4755-ADF6-FC6915583B01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2AE235-CEE7-4082-8D0F-2967070F348E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8841A449-B5A4-4350-BFCF-745781B78CE1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{8841A449-B5A4-4350-BFCF-745781B78CE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Validation" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
   <si>
     <t>Qty:</t>
   </si>
@@ -172,6 +172,9 @@
   </si>
   <si>
     <t>Index-Match Merged</t>
+  </si>
+  <si>
+    <t>We can't get this column using VLOOKUP</t>
   </si>
 </sst>
 </file>
@@ -222,7 +225,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -262,6 +265,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -344,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -364,7 +373,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -768,7 +780,7 @@
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="17">
+      <c r="D3" s="6">
         <v>10</v>
       </c>
       <c r="E3" s="1"/>
@@ -778,7 +790,7 @@
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="17">
+      <c r="D4" s="6">
         <v>15.5</v>
       </c>
       <c r="E4" s="1"/>
@@ -788,7 +800,7 @@
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="17"/>
+      <c r="D5" s="6"/>
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
@@ -796,7 +808,7 @@
       <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="17"/>
+      <c r="D6" s="6"/>
       <c r="E6" s="1"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
@@ -804,7 +816,7 @@
       <c r="C7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="17"/>
+      <c r="D7" s="6"/>
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
@@ -1003,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32702AAF-D203-49B6-B2C2-C7513BD0F1DC}">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.77734375" bestFit="1" customWidth="1"/>
@@ -1046,6 +1058,17 @@
       <c r="B2">
         <v>2590</v>
       </c>
+      <c r="C2">
+        <f>VLOOKUP(A2,Population!$B$1:$D$7,3,FALSE)</f>
+        <v>68.7</v>
+      </c>
+      <c r="E2">
+        <f>VLOOKUP(A2, Population!$B$2:$F$7, 5,FALSE)</f>
+        <v>75.53</v>
+      </c>
+      <c r="F2" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1053,6 +1076,14 @@
       </c>
       <c r="B3">
         <v>3196</v>
+      </c>
+      <c r="C3">
+        <f>VLOOKUP(A3,Population!$B$1:$D$7,3,FALSE)</f>
+        <v>68.8</v>
+      </c>
+      <c r="E3">
+        <f>VLOOKUP(A3, Population!$B$2:$F$7, 5,FALSE)</f>
+        <v>40</v>
       </c>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
@@ -1066,12 +1097,20 @@
       <c r="B4">
         <v>2400</v>
       </c>
+      <c r="C4">
+        <f>VLOOKUP(A4,Population!$B$1:$D$7,3,FALSE)</f>
+        <v>64.900000000000006</v>
+      </c>
+      <c r="E4">
+        <f>VLOOKUP(A4, Population!$B$2:$F$7, 5,FALSE)</f>
+        <v>38.799999999999997</v>
+      </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7" t="s">
         <v>5</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K4" s="7"/>
     </row>
@@ -1082,6 +1121,14 @@
       <c r="B5">
         <v>2530</v>
       </c>
+      <c r="C5">
+        <f>VLOOKUP(A5,Population!$B$1:$D$7,3,FALSE)</f>
+        <v>72.3</v>
+      </c>
+      <c r="E5">
+        <f>VLOOKUP(A5, Population!$B$2:$F$7, 5,FALSE)</f>
+        <v>61.05</v>
+      </c>
       <c r="H5" s="7"/>
       <c r="I5" s="7" t="s">
         <v>16</v>
@@ -1096,6 +1143,14 @@
       <c r="B6">
         <v>2900</v>
       </c>
+      <c r="C6">
+        <f>VLOOKUP(A6,Population!$B$1:$D$7,3,FALSE)</f>
+        <v>52.2</v>
+      </c>
+      <c r="E6">
+        <f>VLOOKUP(A6, Population!$B$2:$F$7, 5,FALSE)</f>
+        <v>34.700000000000003</v>
+      </c>
       <c r="H6" s="7"/>
       <c r="I6" s="7" t="s">
         <v>28</v>
@@ -1109,6 +1164,14 @@
       </c>
       <c r="B7">
         <v>2850</v>
+      </c>
+      <c r="C7">
+        <f>VLOOKUP(A7,Population!$B$1:$D$7,3,FALSE)</f>
+        <v>60.5</v>
+      </c>
+      <c r="E7">
+        <f>VLOOKUP(A7, Population!$B$2:$F$7, 5,FALSE)</f>
+        <v>62.2</v>
       </c>
       <c r="H7" s="7"/>
       <c r="I7" s="7" t="s">
@@ -1141,129 +1204,163 @@
       </c>
       <c r="E11" s="16"/>
     </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14">
+        <f>MATCH(B13,A2:A7,0)</f>
+        <v>2</v>
+      </c>
+      <c r="D14" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" t="str">
+        <f>INDEX(A2:A7, E13)</f>
+        <v>Surat</v>
+      </c>
+      <c r="F14" t="str">
+        <f>INDEX(B1:F1, 3)</f>
+        <v>Population</v>
+      </c>
+    </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" t="s">
-        <v>14</v>
-      </c>
-      <c r="D15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15">
-        <v>6</v>
+      <c r="D15" s="14" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
       </c>
       <c r="D16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17">
+        <f>MATCH(B16, A1:F1, 0)</f>
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E17">
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D17" s="14" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18">
+        <f>INDEX(A1:F7, E16, E17)</f>
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="F22" t="s">
+        <v>45</v>
+      </c>
+      <c r="G22">
+        <f>MATCH(C22, A2:A7,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C23" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D18" t="s">
-        <v>21</v>
-      </c>
-      <c r="E18">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>40</v>
-      </c>
-      <c r="D19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="D20" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
       <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F23" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23">
+        <f>MATCH(C23, B1:F1,0)</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="2"/>
       <c r="B24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>13</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C24" s="5"/>
       <c r="D24" s="2"/>
-      <c r="F24" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
       <c r="B25" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>6</v>
+        <v>44</v>
+      </c>
+      <c r="C25" s="15">
+        <f>INDEX(B2:F7,G22,G23)</f>
+        <v>52.2</v>
       </c>
       <c r="D25" s="2"/>
-      <c r="F25" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="2"/>
       <c r="B26" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="5"/>
+        <v>47</v>
+      </c>
+      <c r="C26" s="15"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="2"/>
-      <c r="B27" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" s="15"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1271,13 +1368,13 @@
     <mergeCell ref="D11:E11"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C25" xr:uid="{FE11E48D-BC8E-4AD7-96F3-F308073CC172}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23" xr:uid="{FE11E48D-BC8E-4AD7-96F3-F308073CC172}">
       <formula1>$A$1:$D$1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C24 J4 B15" xr:uid="{D1AF33DB-32AB-4D38-869B-BE134C3B46C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C22 J4 B13" xr:uid="{D1AF33DB-32AB-4D38-869B-BE134C3B46C2}">
       <formula1>$A$2:$A$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B18" xr:uid="{164EC93F-871D-41DF-9C1E-70006FCA150B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B16" xr:uid="{164EC93F-871D-41DF-9C1E-70006FCA150B}">
       <formula1>$B$1:$E$1</formula1>
     </dataValidation>
   </dataValidations>
@@ -1287,16 +1384,17 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A5EB3AB-EDCB-4C4F-89B8-2F0BD2EA93E2}">
-  <dimension ref="B3:E13"/>
+  <dimension ref="B3:H13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
         <v>29</v>
       </c>
@@ -1309,8 +1407,14 @@
       <c r="E3" s="12" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="4" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G3" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
         <v>33</v>
       </c>
@@ -1323,8 +1427,15 @@
       <c r="E4" s="8">
         <v>98</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G4" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="6">
+        <f>HLOOKUP(H3,C3:E7,4,FALSE)</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
         <v>34</v>
       </c>
@@ -1337,8 +1448,12 @@
       <c r="E5" s="8">
         <v>21</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="6"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
@@ -1352,7 +1467,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="8" t="s">
         <v>36</v>
       </c>
@@ -1366,7 +1481,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="8" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
         <v>37</v>
       </c>
@@ -1380,25 +1495,30 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
       <c r="C11" s="13"/>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="10" t="s">
         <v>25</v>
       </c>
       <c r="C12" s="13"/>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="13"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3" xr:uid="{4116607F-BA89-4104-BC26-1A6B693291F7}">
+      <formula1>$C$3:$E$3</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>

--- a/2024AIDataScienceGNRGeneral/Advanced Excel/jan25.xlsx
+++ b/2024AIDataScienceGNRGeneral/Advanced Excel/jan25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\2024AIDataScienceGNRGeneral\Advanced Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E2AE235-CEE7-4082-8D0F-2967070F348E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321F08D5-8002-486E-8F29-753C37C486BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{8841A449-B5A4-4350-BFCF-745781B78CE1}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{8841A449-B5A4-4350-BFCF-745781B78CE1}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Validation" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="49">
   <si>
     <t>Qty:</t>
   </si>
@@ -370,12 +370,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1195,14 +1195,14 @@
       <c r="K9" s="7"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="16"/>
-      <c r="D11" s="16" t="s">
+      <c r="B11" s="18"/>
+      <c r="D11" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="E11" s="16"/>
+      <c r="E11" s="18"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1239,6 +1239,10 @@
       <c r="F14" t="str">
         <f>INDEX(B1:F1, 3)</f>
         <v>Population</v>
+      </c>
+      <c r="H14">
+        <f>INDEX(A1:E7, 3, 4)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -1353,7 +1357,10 @@
       <c r="B26" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C26" s="15"/>
+      <c r="C26" s="15">
+        <f>INDEX(A1:E7, MATCH(C22, A1:A7, 0), MATCH(C23, A1:E1, 0))</f>
+        <v>52.2</v>
+      </c>
       <c r="D26" s="2"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1407,10 +1414,10 @@
       <c r="E3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="17" t="s">
+      <c r="G3" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="H3" s="18" t="s">
+      <c r="H3" s="17" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1427,7 +1434,7 @@
       <c r="E4" s="8">
         <v>98</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="G4" s="16" t="s">
         <v>35</v>
       </c>
       <c r="H4" s="6">
@@ -1448,7 +1455,7 @@
       <c r="E5" s="8">
         <v>21</v>
       </c>
-      <c r="G5" s="17" t="s">
+      <c r="G5" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H5" s="6"/>
@@ -1499,24 +1506,34 @@
       <c r="B11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="13"/>
+      <c r="C11" s="13" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="C12" s="13"/>
+      <c r="C12" s="13" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="13"/>
+      <c r="C13" s="13">
+        <f>IFERROR(INDEX(Table_57[#All],MATCH(C12,Table_57[[#All],[Name]],0),MATCH(C11,Table_57[#Headers],0)), "Please select Batsman &amp; Parameter both.")</f>
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3" xr:uid="{4116607F-BA89-4104-BC26-1A6B693291F7}">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3 C11" xr:uid="{4116607F-BA89-4104-BC26-1A6B693291F7}">
       <formula1>$C$3:$E$3</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{7CD04B4F-F822-4C9B-9545-58DDADD3EFF3}">
+      <formula1>$B$4:$B$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
